--- a/Assets/Resources/Excel/Sound.xlsx
+++ b/Assets/Resources/Excel/Sound.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC742D0-B512-4DEF-BEC2-AD15E13F9ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EF15E1-896D-452B-BAC8-F8AB23C84337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2145" yWindow="1185" windowWidth="21480" windowHeight="13380" xr2:uid="{390C7208-66F1-497C-8CC9-7C965485B0DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{390C7208-66F1-497C-8CC9-7C965485B0DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1518,7 +1518,7 @@
         <v>59</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -1535,7 +1535,7 @@
         <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1552,7 +1552,7 @@
         <v>61</v>
       </c>
       <c r="C56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -1569,7 +1569,7 @@
         <v>62</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1586,7 +1586,7 @@
         <v>63</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -1603,7 +1603,7 @@
         <v>64</v>
       </c>
       <c r="C59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59">
         <v>1</v>

--- a/Assets/Resources/Excel/Sound.xlsx
+++ b/Assets/Resources/Excel/Sound.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7EF15E1-896D-452B-BAC8-F8AB23C84337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A7DF4E-3FD5-461E-897A-959DEB1D2564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{390C7208-66F1-497C-8CC9-7C965485B0DB}"/>
+    <workbookView xWindow="2145" yWindow="1185" windowWidth="21480" windowHeight="13380" xr2:uid="{390C7208-66F1-497C-8CC9-7C965485B0DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -607,6 +607,8 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,7 +1234,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>

--- a/Assets/Resources/Excel/Sound.xlsx
+++ b/Assets/Resources/Excel/Sound.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A7DF4E-3FD5-461E-897A-959DEB1D2564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F6A6A7-8CA0-4BA6-9ABD-8921A61DC2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="1185" windowWidth="21480" windowHeight="13380" xr2:uid="{390C7208-66F1-497C-8CC9-7C965485B0DB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="66">
   <si>
     <t>AudioID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -240,6 +240,10 @@
   </si>
   <si>
     <t>Indoor_GunshotPistol_3</t>
+  </si>
+  <si>
+    <t>AMBIENT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -874,7 +878,7 @@
         <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -891,7 +895,7 @@
         <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -925,7 +929,7 @@
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D19">
         <v>1</v>

--- a/Assets/Resources/Excel/Sound.xlsx
+++ b/Assets/Resources/Excel/Sound.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F6A6A7-8CA0-4BA6-9ABD-8921A61DC2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED1A279-FFE7-4DAA-8C61-F94FF764D7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="1185" windowWidth="21480" windowHeight="13380" xr2:uid="{390C7208-66F1-497C-8CC9-7C965485B0DB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="75">
   <si>
     <t>AudioID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -244,6 +244,35 @@
   <si>
     <t>AMBIENT</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BGM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Divers</t>
+  </si>
+  <si>
+    <t>Extraction_Failed</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>Lobby_1</t>
+  </si>
+  <si>
+    <t>Pre-Extraction Sequence_1</t>
+  </si>
+  <si>
+    <t>Title_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Victroy_1</t>
+  </si>
+  <si>
+    <t>Yuan_Memory</t>
   </si>
 </sst>
 </file>
@@ -607,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA92F57-20FC-47F2-9478-340152432242}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.625" bestFit="1" customWidth="1"/>
@@ -634,146 +663,146 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>10101</v>
+        <v>10001</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>10102</v>
+        <v>10002</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>10103</v>
+        <v>10003</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>10104</v>
+        <v>10004</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>10105</v>
+        <v>10005</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>10106</v>
+        <v>10006</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>10107</v>
+        <v>10007</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>10108</v>
+        <v>10008</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>10201</v>
+        <v>10101</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -787,10 +816,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10202</v>
+        <v>10102</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -804,10 +833,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>10203</v>
+        <v>10103</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -821,10 +850,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>10204</v>
+        <v>10104</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -838,10 +867,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>10205</v>
+        <v>10105</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -855,10 +884,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>10206</v>
+        <v>10106</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -872,44 +901,44 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>10301</v>
+        <v>10107</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>10302</v>
+        <v>10108</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>10303</v>
+        <v>10201</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -923,27 +952,27 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>10304</v>
+        <v>10202</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>10305</v>
+        <v>10203</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -952,15 +981,15 @@
         <v>1</v>
       </c>
       <c r="E20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>10401</v>
+        <v>10204</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -969,15 +998,15 @@
         <v>1</v>
       </c>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>10402</v>
+        <v>10205</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -986,15 +1015,15 @@
         <v>1</v>
       </c>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>10403</v>
+        <v>10206</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -1008,44 +1037,44 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>10404</v>
+        <v>10301</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>10501</v>
+        <v>10302</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>10502</v>
+        <v>10303</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -1059,27 +1088,27 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>10503</v>
+        <v>10304</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>10504</v>
+        <v>10305</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -1088,15 +1117,15 @@
         <v>1</v>
       </c>
       <c r="E28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>10505</v>
+        <v>10401</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -1105,15 +1134,15 @@
         <v>1</v>
       </c>
       <c r="E29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>10506</v>
+        <v>10402</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -1122,15 +1151,15 @@
         <v>1</v>
       </c>
       <c r="E30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>10507</v>
+        <v>10403</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1144,10 +1173,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>10508</v>
+        <v>10404</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -1161,10 +1190,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>10509</v>
+        <v>10501</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1178,10 +1207,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>10510</v>
+        <v>10502</v>
       </c>
       <c r="B34" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1195,10 +1224,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>10601</v>
+        <v>10503</v>
       </c>
       <c r="B35" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1212,10 +1241,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>10602</v>
+        <v>10504</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1229,27 +1258,27 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>10603</v>
+        <v>10505</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
       </c>
       <c r="D37">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>10701</v>
+        <v>10506</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1263,10 +1292,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>10702</v>
+        <v>10507</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1280,10 +1309,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>10703</v>
+        <v>10508</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -1297,10 +1326,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>10704</v>
+        <v>10509</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -1314,10 +1343,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>10705</v>
+        <v>10510</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1331,10 +1360,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>10706</v>
+        <v>10601</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -1348,10 +1377,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>10801</v>
+        <v>10602</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1360,35 +1389,35 @@
         <v>1</v>
       </c>
       <c r="E44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>10901</v>
+        <v>10603</v>
       </c>
       <c r="B45" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>10902</v>
+        <v>10701</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -1399,13 +1428,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>10903</v>
+        <v>10702</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -1416,13 +1445,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>10904</v>
+        <v>10703</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1433,13 +1462,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>10905</v>
+        <v>10704</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1450,13 +1479,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>10906</v>
+        <v>10705</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1467,13 +1496,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>10907</v>
+        <v>10706</v>
       </c>
       <c r="B51" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -1484,27 +1513,27 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>10908</v>
+        <v>10801</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>10909</v>
+        <v>10901</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
         <v>6</v>
@@ -1518,13 +1547,13 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>11001</v>
+        <v>10902</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -1535,13 +1564,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>11002</v>
+        <v>10903</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1552,13 +1581,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>11003</v>
+        <v>10904</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -1569,13 +1598,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>11004</v>
+        <v>10905</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1586,13 +1615,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>11005</v>
+        <v>10906</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -1603,18 +1632,154 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
+        <v>10907</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59">
+        <v>1</v>
+      </c>
+      <c r="E59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>10908</v>
+      </c>
+      <c r="B60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60">
+        <v>1</v>
+      </c>
+      <c r="E60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>10909</v>
+      </c>
+      <c r="B61" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>11001</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>11002</v>
+      </c>
+      <c r="B63" t="s">
+        <v>60</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="E63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>11003</v>
+      </c>
+      <c r="B64" t="s">
+        <v>61</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>11004</v>
+      </c>
+      <c r="B65" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65">
+        <v>1</v>
+      </c>
+      <c r="E65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>11005</v>
+      </c>
+      <c r="B66" t="s">
+        <v>63</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>1</v>
+      </c>
+      <c r="E66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67">
         <v>11006</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B67" t="s">
         <v>64</v>
       </c>
-      <c r="C59" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59" t="b">
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Sound.xlsx
+++ b/Assets/Resources/Excel/Sound.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED1A279-FFE7-4DAA-8C61-F94FF764D7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85443220-68F4-49A3-9DEA-2E704BE852E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="1185" windowWidth="21480" windowHeight="13380" xr2:uid="{390C7208-66F1-497C-8CC9-7C965485B0DB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
   <si>
     <t>AudioID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>Yuan_Memory</t>
+  </si>
+  <si>
+    <t>InGame_Embient_2</t>
   </si>
 </sst>
 </file>
@@ -636,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA92F57-20FC-47F2-9478-340152432242}">
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.625" bestFit="1" customWidth="1"/>
@@ -1122,13 +1125,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>10401</v>
+        <v>10306</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1139,10 +1142,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>10402</v>
+        <v>10401</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -1156,10 +1159,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>10403</v>
+        <v>10402</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1168,15 +1171,15 @@
         <v>1</v>
       </c>
       <c r="E31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>10404</v>
+        <v>10403</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -1190,10 +1193,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>10501</v>
+        <v>10404</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1207,10 +1210,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>10502</v>
+        <v>10501</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1224,10 +1227,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>10503</v>
+        <v>10502</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1241,10 +1244,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>10504</v>
+        <v>10503</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1258,10 +1261,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>10505</v>
+        <v>10504</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1275,10 +1278,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>10506</v>
+        <v>10505</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1292,10 +1295,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>10507</v>
+        <v>10506</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1309,10 +1312,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>10508</v>
+        <v>10507</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -1326,10 +1329,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>10509</v>
+        <v>10508</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -1343,10 +1346,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>10510</v>
+        <v>10509</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1360,10 +1363,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>10601</v>
+        <v>10510</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -1377,10 +1380,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>10602</v>
+        <v>10601</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1394,44 +1397,44 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>10603</v>
+        <v>10602</v>
       </c>
       <c r="B45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
       </c>
       <c r="D45">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>10701</v>
+        <v>10603</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>10702</v>
+        <v>10701</v>
       </c>
       <c r="B47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -1445,10 +1448,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>10703</v>
+        <v>10702</v>
       </c>
       <c r="B48" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -1462,10 +1465,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>10704</v>
+        <v>10703</v>
       </c>
       <c r="B49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -1479,10 +1482,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>10705</v>
+        <v>10704</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1496,10 +1499,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>10706</v>
+        <v>10705</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1513,10 +1516,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>10801</v>
+        <v>10706</v>
       </c>
       <c r="B52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -1525,32 +1528,32 @@
         <v>1</v>
       </c>
       <c r="E52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>10901</v>
+        <v>10801</v>
       </c>
       <c r="B53" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53">
         <v>1</v>
       </c>
       <c r="E53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>10902</v>
+        <v>10901</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
         <v>6</v>
@@ -1564,10 +1567,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>10903</v>
+        <v>10902</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C55" t="s">
         <v>6</v>
@@ -1581,10 +1584,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>10904</v>
+        <v>10903</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
         <v>6</v>
@@ -1598,10 +1601,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>10905</v>
+        <v>10904</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
         <v>6</v>
@@ -1615,10 +1618,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>10906</v>
+        <v>10905</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C58" t="s">
         <v>6</v>
@@ -1632,10 +1635,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>10907</v>
+        <v>10906</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
         <v>6</v>
@@ -1649,10 +1652,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>10908</v>
+        <v>10907</v>
       </c>
       <c r="B60" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C60" t="s">
         <v>6</v>
@@ -1666,10 +1669,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>10909</v>
+        <v>10908</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C61" t="s">
         <v>6</v>
@@ -1683,13 +1686,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>11001</v>
+        <v>10909</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -1700,10 +1703,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1717,10 +1720,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="B64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1734,10 +1737,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1751,10 +1754,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1768,18 +1771,35 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
+        <v>11005</v>
+      </c>
+      <c r="B67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68">
         <v>11006</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
         <v>64</v>
       </c>
-      <c r="C67" t="s">
-        <v>5</v>
-      </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67" t="b">
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Sound.xlsx
+++ b/Assets/Resources/Excel/Sound.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Woo_260126\UnityProject_LucidDiver\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85443220-68F4-49A3-9DEA-2E704BE852E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB456B8-83FB-475E-B726-737847F14897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2145" yWindow="1185" windowWidth="21480" windowHeight="13380" xr2:uid="{390C7208-66F1-497C-8CC9-7C965485B0DB}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="77">
   <si>
     <t>AudioID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -276,6 +276,10 @@
   </si>
   <si>
     <t>InGame_Embient_2</t>
+  </si>
+  <si>
+    <t>PayPhoneRing_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -639,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FA92F57-20FC-47F2-9478-340152432242}">
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.625" bestFit="1" customWidth="1"/>
@@ -1142,13 +1146,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>10401</v>
+        <v>10307</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1159,10 +1163,10 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>10402</v>
+        <v>10401</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1176,10 +1180,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>10403</v>
+        <v>10402</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -1188,15 +1192,15 @@
         <v>1</v>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>10404</v>
+        <v>10403</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1210,10 +1214,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>10501</v>
+        <v>10404</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1227,10 +1231,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>10502</v>
+        <v>10501</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1244,10 +1248,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>10503</v>
+        <v>10502</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1261,10 +1265,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>10504</v>
+        <v>10503</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1278,10 +1282,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>10505</v>
+        <v>10504</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1295,10 +1299,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>10506</v>
+        <v>10505</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1312,10 +1316,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>10507</v>
+        <v>10506</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -1329,10 +1333,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>10508</v>
+        <v>10507</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -1346,10 +1350,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>10509</v>
+        <v>10508</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1363,10 +1367,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>10510</v>
+        <v>10509</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -1380,10 +1384,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>10601</v>
+        <v>10510</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1397,10 +1401,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>10602</v>
+        <v>10601</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -1414,44 +1418,44 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>10603</v>
+        <v>10602</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="D46">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="E46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>10701</v>
+        <v>10603</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>10702</v>
+        <v>10701</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -1465,10 +1469,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>10703</v>
+        <v>10702</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -1482,10 +1486,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>10704</v>
+        <v>10703</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1499,10 +1503,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>10705</v>
+        <v>10704</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1516,10 +1520,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>10706</v>
+        <v>10705</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -1533,10 +1537,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>10801</v>
+        <v>10706</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -1545,32 +1549,32 @@
         <v>1</v>
       </c>
       <c r="E53" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>10901</v>
+        <v>10801</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
       <c r="E54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>10902</v>
+        <v>10901</v>
       </c>
       <c r="B55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
         <v>6</v>
@@ -1584,10 +1588,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>10903</v>
+        <v>10902</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C56" t="s">
         <v>6</v>
@@ -1601,10 +1605,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>10904</v>
+        <v>10903</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
         <v>6</v>
@@ -1618,10 +1622,10 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>10905</v>
+        <v>10904</v>
       </c>
       <c r="B58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
         <v>6</v>
@@ -1635,10 +1639,10 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>10906</v>
+        <v>10905</v>
       </c>
       <c r="B59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C59" t="s">
         <v>6</v>
@@ -1652,10 +1656,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>10907</v>
+        <v>10906</v>
       </c>
       <c r="B60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
         <v>6</v>
@@ -1669,10 +1673,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>10908</v>
+        <v>10907</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
         <v>6</v>
@@ -1686,10 +1690,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>10909</v>
+        <v>10908</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
         <v>6</v>
@@ -1703,13 +1707,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>11001</v>
+        <v>10909</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -1720,10 +1724,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="B64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1737,10 +1741,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="B65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1754,10 +1758,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1771,10 +1775,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -1788,18 +1792,35 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68">
+        <v>11005</v>
+      </c>
+      <c r="B68" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69">
         <v>11006</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>64</v>
       </c>
-      <c r="C68" t="s">
-        <v>5</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68" t="b">
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>1</v>
+      </c>
+      <c r="E69" t="b">
         <v>0</v>
       </c>
     </row>
